--- a/artfynd/A 47172-2023 artfynd.xlsx
+++ b/artfynd/A 47172-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47172-2023 artfynd.xlsx
+++ b/artfynd/A 47172-2023 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62025658</v>
+        <v>62025655</v>
       </c>
       <c r="B2" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6463</v>
+        <v>3286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>547335.4203044928</v>
+        <v>547335</v>
       </c>
       <c r="R2" t="n">
-        <v>6984007.165199152</v>
+        <v>6984007</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-09-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Grov sälg</t>
+          <t>Lövrik mark</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62025655</v>
+        <v>62025656</v>
       </c>
       <c r="B3" t="n">
-        <v>88886</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3286</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>547335.4203044928</v>
+        <v>547335</v>
       </c>
       <c r="R3" t="n">
-        <v>6984007.165199152</v>
+        <v>6984007</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2016-09-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Lövrik mark</t>
+          <t>Grov sälg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -922,12 +892,7 @@
         <v>62025657</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>547335.4203044928</v>
+        <v>547335</v>
       </c>
       <c r="R4" t="n">
-        <v>6984007.165199152</v>
+        <v>6984007</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2016-09-03</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62025656</v>
+        <v>62025658</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>547335.4203044928</v>
+        <v>547335</v>
       </c>
       <c r="R5" t="n">
-        <v>6984007.165199152</v>
+        <v>6984007</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,19 +1064,9 @@
           <t>2016-09-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-09-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47172-2023 artfynd.xlsx
+++ b/artfynd/A 47172-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025655</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025657</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,8 +1120,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62025658</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>